--- a/results/stat_validation/stat_validation_results.xlsx
+++ b/results/stat_validation/stat_validation_results.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:J18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -472,10 +472,15 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>KPSS p</t>
+          <t>KPSS стат.</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>KPSS 5%крит.</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Стационарен</t>
         </is>
@@ -510,9 +515,12 @@
         <v>7.336178322743143e-26</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I2" t="inlineStr">
+        <v>0.09851239237527434</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.463</v>
+      </c>
+      <c r="J2" t="inlineStr">
         <is>
           <t>да</t>
         </is>
@@ -547,9 +555,12 @@
         <v>3.173791761707487e-21</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I3" t="inlineStr">
+        <v>0.1250650421332226</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.463</v>
+      </c>
+      <c r="J3" t="inlineStr">
         <is>
           <t>да</t>
         </is>
@@ -584,9 +595,12 @@
         <v>9.229651978841096e-23</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I4" t="inlineStr">
+        <v>0.07499836530674987</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.463</v>
+      </c>
+      <c r="J4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
@@ -621,9 +635,12 @@
         <v>6.007699766783726e-27</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I5" t="inlineStr">
+        <v>0.103302631319219</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.463</v>
+      </c>
+      <c r="J5" t="inlineStr">
         <is>
           <t>да</t>
         </is>
@@ -658,9 +675,12 @@
         <v>7.325212969110181e-18</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I6" t="inlineStr">
+        <v>0.07898691221742793</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.463</v>
+      </c>
+      <c r="J6" t="inlineStr">
         <is>
           <t>да</t>
         </is>
@@ -695,9 +715,12 @@
         <v>1.067642964377715e-23</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I7" t="inlineStr">
+        <v>0.05009520973115591</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.463</v>
+      </c>
+      <c r="J7" t="inlineStr">
         <is>
           <t>да</t>
         </is>
@@ -732,9 +755,12 @@
         <v>3.011881543839573e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I8" t="inlineStr">
+        <v>0.07448726827994888</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.463</v>
+      </c>
+      <c r="J8" t="inlineStr">
         <is>
           <t>да</t>
         </is>
@@ -769,9 +795,12 @@
         <v>0.008358293684754376</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I9" t="inlineStr">
+        <v>0.07373408982906712</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.463</v>
+      </c>
+      <c r="J9" t="inlineStr">
         <is>
           <t>да</t>
         </is>
@@ -806,9 +835,12 @@
         <v>2.037562730476009e-05</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I10" t="inlineStr">
+        <v>0.08249150655566828</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.463</v>
+      </c>
+      <c r="J10" t="inlineStr">
         <is>
           <t>да</t>
         </is>
@@ -843,9 +875,12 @@
         <v>1.643671900988065e-23</v>
       </c>
       <c r="H11" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I11" t="inlineStr">
+        <v>0.04876417407885773</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.463</v>
+      </c>
+      <c r="J11" t="inlineStr">
         <is>
           <t>да</t>
         </is>
@@ -880,9 +915,12 @@
         <v>0.0001425672344858739</v>
       </c>
       <c r="H12" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I12" t="inlineStr">
+        <v>0.0911137081413006</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.463</v>
+      </c>
+      <c r="J12" t="inlineStr">
         <is>
           <t>да</t>
         </is>
@@ -917,9 +955,12 @@
         <v>2.103229398214185e-21</v>
       </c>
       <c r="H13" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I13" t="inlineStr">
+        <v>0.1610328959132439</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.463</v>
+      </c>
+      <c r="J13" t="inlineStr">
         <is>
           <t>да</t>
         </is>
@@ -954,9 +995,12 @@
         <v>5.750524081197171e-25</v>
       </c>
       <c r="H14" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I14" t="inlineStr">
+        <v>0.1558875020313172</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.463</v>
+      </c>
+      <c r="J14" t="inlineStr">
         <is>
           <t>да</t>
         </is>
@@ -991,9 +1035,12 @@
         <v>4.252358359314191e-07</v>
       </c>
       <c r="H15" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I15" t="inlineStr">
+        <v>0.07741490816386247</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.463</v>
+      </c>
+      <c r="J15" t="inlineStr">
         <is>
           <t>да</t>
         </is>
@@ -1028,9 +1075,12 @@
         <v>1.603175066080513e-21</v>
       </c>
       <c r="H16" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I16" t="inlineStr">
+        <v>0.04708077199784309</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.463</v>
+      </c>
+      <c r="J16" t="inlineStr">
         <is>
           <t>да</t>
         </is>
@@ -1065,9 +1115,12 @@
         <v>1.001063786993808e-24</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I17" t="inlineStr">
+        <v>0.06370012412807782</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.463</v>
+      </c>
+      <c r="J17" t="inlineStr">
         <is>
           <t>да</t>
         </is>
@@ -1102,9 +1155,12 @@
         <v>5.554341870137192e-26</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I18" t="inlineStr">
+        <v>0.04506306631900989</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.463</v>
+      </c>
+      <c r="J18" t="inlineStr">
         <is>
           <t>да</t>
         </is>
@@ -2273,7 +2329,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:J18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2314,10 +2370,15 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>KPSS p</t>
+          <t>KPSS стат.</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>KPSS 5%крит.</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Стационарен</t>
         </is>
@@ -2352,9 +2413,12 @@
         <v>2.880728513033746e-22</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I2" t="inlineStr">
+        <v>0.1292738365649255</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.463</v>
+      </c>
+      <c r="J2" t="inlineStr">
         <is>
           <t>да</t>
         </is>
@@ -2389,9 +2453,12 @@
         <v>6.119331071950884e-21</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I3" t="inlineStr">
+        <v>0.1172766049327004</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.463</v>
+      </c>
+      <c r="J3" t="inlineStr">
         <is>
           <t>да</t>
         </is>
@@ -2426,9 +2493,12 @@
         <v>2.152592932882202e-23</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I4" t="inlineStr">
+        <v>0.07434967099844904</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.463</v>
+      </c>
+      <c r="J4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
@@ -2463,9 +2533,12 @@
         <v>2.935990532587355e-26</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I5" t="inlineStr">
+        <v>0.1838891783087192</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.463</v>
+      </c>
+      <c r="J5" t="inlineStr">
         <is>
           <t>да</t>
         </is>
@@ -2500,9 +2573,12 @@
         <v>1.153945232653832e-24</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I6" t="inlineStr">
+        <v>0.1638889110775939</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.463</v>
+      </c>
+      <c r="J6" t="inlineStr">
         <is>
           <t>да</t>
         </is>
@@ -2537,9 +2613,12 @@
         <v>2.30835463659211e-21</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I7" t="inlineStr">
+        <v>0.1724347927018777</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.463</v>
+      </c>
+      <c r="J7" t="inlineStr">
         <is>
           <t>да</t>
         </is>
@@ -2574,9 +2653,12 @@
         <v>9.09688148282496e-25</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I8" t="inlineStr">
+        <v>0.09132264216412848</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.463</v>
+      </c>
+      <c r="J8" t="inlineStr">
         <is>
           <t>да</t>
         </is>
@@ -2611,9 +2693,12 @@
         <v>3.31360014578215e-23</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I9" t="inlineStr">
+        <v>0.1009040839637905</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.463</v>
+      </c>
+      <c r="J9" t="inlineStr">
         <is>
           <t>да</t>
         </is>
@@ -2648,9 +2733,12 @@
         <v>7.874537165816845e-24</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I10" t="inlineStr">
+        <v>0.07930088719718721</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.463</v>
+      </c>
+      <c r="J10" t="inlineStr">
         <is>
           <t>да</t>
         </is>
@@ -2685,9 +2773,12 @@
         <v>3.528697765686858e-22</v>
       </c>
       <c r="H11" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I11" t="inlineStr">
+        <v>0.2617325490132136</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.463</v>
+      </c>
+      <c r="J11" t="inlineStr">
         <is>
           <t>да</t>
         </is>
@@ -2722,9 +2813,12 @@
         <v>9.268517961193748e-26</v>
       </c>
       <c r="H12" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I12" t="inlineStr">
+        <v>0.1816461385347821</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.463</v>
+      </c>
+      <c r="J12" t="inlineStr">
         <is>
           <t>да</t>
         </is>
@@ -2759,9 +2853,12 @@
         <v>1.36216957959553e-21</v>
       </c>
       <c r="H13" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I13" t="inlineStr">
+        <v>0.1168180892940317</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.463</v>
+      </c>
+      <c r="J13" t="inlineStr">
         <is>
           <t>да</t>
         </is>
@@ -2796,9 +2893,12 @@
         <v>8.641514393072109e-22</v>
       </c>
       <c r="H14" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I14" t="inlineStr">
+        <v>0.084959265094544</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.463</v>
+      </c>
+      <c r="J14" t="inlineStr">
         <is>
           <t>да</t>
         </is>
@@ -2833,9 +2933,12 @@
         <v>3.05771446714801e-17</v>
       </c>
       <c r="H15" t="n">
-        <v>0.06582474423930613</v>
-      </c>
-      <c r="I15" t="inlineStr">
+        <v>0.4262865933648098</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.463</v>
+      </c>
+      <c r="J15" t="inlineStr">
         <is>
           <t>да</t>
         </is>
@@ -2870,9 +2973,12 @@
         <v>2.811876203287656e-23</v>
       </c>
       <c r="H16" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I16" t="inlineStr">
+        <v>0.1085558457554537</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.463</v>
+      </c>
+      <c r="J16" t="inlineStr">
         <is>
           <t>да</t>
         </is>
@@ -2907,9 +3013,12 @@
         <v>1.098269420552562e-22</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I17" t="inlineStr">
+        <v>0.1194262037769843</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.463</v>
+      </c>
+      <c r="J17" t="inlineStr">
         <is>
           <t>да</t>
         </is>
@@ -2944,9 +3053,12 @@
         <v>1.510481241877441e-22</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I18" t="inlineStr">
+        <v>0.09503697028942426</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.463</v>
+      </c>
+      <c r="J18" t="inlineStr">
         <is>
           <t>да</t>
         </is>
